--- a/strumenti/anomalie-28ago.xlsx
+++ b/strumenti/anomalie-28ago.xlsx
@@ -11,10 +11,9 @@
     <sheet name="5 In ritardo" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'1 Stati'!A1:J9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'2 Spedizioni'!A1:J5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'1 Stati'!A1:J14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'3 Senza codice'!A1:I5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'5 In ritardo'!A1:I7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'5 In ritardo'!A1:I5</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -442,7 +441,7 @@
         <v>Estrazione Alnus del</v>
       </c>
       <c r="B3" t="str">
-        <v>27/08/2026 15:57</v>
+        <v>28/08/2026 14:59</v>
       </c>
       <c r="C3" t="str">
         <v>Quello che hai sistemato IN ALNUS dopo quest’ora NON si vede: serve una nuova estrazione.</v>
@@ -453,7 +452,7 @@
         <v>Righe nel file</v>
       </c>
       <c r="B4">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C4" t="str">
         <v>Solo sezionale OC; gli OD restano fuori.</v>
@@ -475,7 +474,7 @@
         <v>1 Stati</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" t="str">
         <v>I due sistemi non concordano su cosa sia finito. E’ il gruppo da sistemare per primo.</v>
@@ -486,7 +485,7 @@
         <v>2 Spedizioni</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7" t="str">
         <v>La quantita’ che resta da evadere non torna fra i due archivi.</v>
@@ -519,7 +518,7 @@
         <v>5 In ritardo</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="str">
         <v>Commesse vive con la scadenza gia’ passata. Non e’ un disaccordo fra i due sistemi.</v>
@@ -544,7 +543,7 @@
         <v>421</v>
       </c>
       <c r="C12" t="str">
-        <v>di cui vive: 135</v>
+        <v>di cui vive: 132</v>
       </c>
     </row>
   </sheetData>
@@ -556,13 +555,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J14"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="36.83203125" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="58.83203125" customWidth="1"/>
@@ -604,25 +603,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026/OC/00136</v>
+        <v>2025/OC/00631</v>
       </c>
       <c r="B2" t="str">
-        <v>0010</v>
+        <v>0050</v>
       </c>
       <c r="C2" t="str">
-        <v>Tema Sinergie S.p.a.</v>
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D2" t="str">
-        <v>TS-341000030</v>
+        <v>SP-TFS01286800</v>
       </c>
       <c r="E2" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F2" t="str">
-        <v>0 / 5</v>
+        <v>0 / 10</v>
       </c>
       <c r="G2" t="str">
-        <v>28/08/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="H2" t="str">
         <v>per Alnus FINITA (sparito tutto l’ordine)</v>
@@ -636,28 +635,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026/OC/00155</v>
+        <v>2025/OC/00631</v>
       </c>
       <c r="B3" t="str">
-        <v>0010</v>
+        <v>0060</v>
       </c>
       <c r="C3" t="str">
         <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D3" t="str">
-        <v>SP-TFS01286800</v>
+        <v>SP-TF1287894</v>
       </c>
       <c r="E3" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F3" t="str">
         <v>0 / 10</v>
       </c>
       <c r="G3" t="str">
-        <v>12/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
       </c>
       <c r="I3" t="str">
         <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
@@ -668,25 +667,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026/OC/00155</v>
+        <v>2026/OC/00154</v>
       </c>
       <c r="B4" t="str">
-        <v>0020</v>
+        <v>0010</v>
       </c>
       <c r="C4" t="str">
         <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D4" t="str">
-        <v>SP-TF1287894</v>
+        <v>SP-TFI01286801</v>
       </c>
       <c r="E4" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F4" t="str">
-        <v>0 / 10</v>
+        <v>0 / 5</v>
       </c>
       <c r="G4" t="str">
-        <v>12/06/2026</v>
+        <v>25/09/2026</v>
       </c>
       <c r="H4" t="str">
         <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
@@ -732,25 +731,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026/OC/00209</v>
+        <v>2026/OC/00174</v>
       </c>
       <c r="B6" t="str">
-        <v>0020</v>
+        <v>0030</v>
       </c>
       <c r="C6" t="str">
         <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D6" t="str">
-        <v>SP-GD2587807</v>
+        <v>SP-TS4386892</v>
       </c>
       <c r="E6" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F6" t="str">
-        <v>0 / 5</v>
+        <v>0 / 10</v>
       </c>
       <c r="G6" t="str">
-        <v>28/08/2026</v>
+        <v>27/08/2026</v>
       </c>
       <c r="H6" t="str">
         <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
@@ -764,28 +763,28 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026/OC/00216</v>
+        <v>2026/OC/00174</v>
       </c>
       <c r="B7" t="str">
-        <v>0010</v>
+        <v>0040</v>
       </c>
       <c r="C7" t="str">
-        <v>Elcotec S.r.l.</v>
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D7" t="str">
-        <v>EL50811EMAN003K3GD40550</v>
+        <v>SP-TS4387813</v>
       </c>
       <c r="E7" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F7" t="str">
-        <v>0 / 30</v>
+        <v>0 / 10</v>
       </c>
       <c r="G7" t="str">
-        <v>30/10/2026</v>
+        <v>27/08/2026</v>
       </c>
       <c r="H7" t="str">
-        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+        <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
       </c>
       <c r="I7" t="str">
         <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
@@ -796,25 +795,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026/OC/00216</v>
+        <v>2026/OC/00179</v>
       </c>
       <c r="B8" t="str">
-        <v>0020</v>
+        <v>0030</v>
       </c>
       <c r="C8" t="str">
-        <v>Elcotec S.r.l.</v>
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D8" t="str">
-        <v>EL50811EMANCR3K3GD41410</v>
+        <v>SP-TSI04386800</v>
       </c>
       <c r="E8" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F8" t="str">
-        <v>0 / 10</v>
+        <v>0 / 8</v>
       </c>
       <c r="G8" t="str">
-        <v>30/10/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="H8" t="str">
         <v>per Alnus FINITA (sparito tutto l’ordine)</v>
@@ -828,25 +827,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026/OC/00329</v>
+        <v>2026/OC/00179</v>
       </c>
       <c r="B9" t="str">
-        <v>0050</v>
+        <v>0040</v>
       </c>
       <c r="C9" t="str">
-        <v>Elcotec S.r.l.</v>
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D9" t="str">
-        <v>EL50811EMAN022K3GD32390</v>
+        <v>SP-TSI04387800</v>
       </c>
       <c r="E9" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F9" t="str">
         <v>0 / 8</v>
       </c>
       <c r="G9" t="str">
-        <v>02/09/2026</v>
+        <v>28/08/2026</v>
       </c>
       <c r="H9" t="str">
         <v>per Alnus FINITA (sparito tutto l’ordine)</v>
@@ -858,194 +857,194 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026/OC/00209</v>
+      </c>
+      <c r="B10" t="str">
+        <v>0020</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>SP-GD2587807</v>
+      </c>
+      <c r="E10" t="str">
+        <v>aperta</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0 / 5</v>
+      </c>
+      <c r="G10" t="str">
+        <v>28/08/2026</v>
+      </c>
+      <c r="H10" t="str">
+        <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026/OC/00216</v>
+      </c>
+      <c r="B11" t="str">
+        <v>0010</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>EL50811EMAN003K3GD40550</v>
+      </c>
+      <c r="E11" t="str">
+        <v>aperta</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0 / 30</v>
+      </c>
+      <c r="G11" t="str">
+        <v>30/10/2026</v>
+      </c>
+      <c r="H11" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026/OC/00216</v>
+      </c>
+      <c r="B12" t="str">
+        <v>0020</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>EL50811EMANCR3K3GD41410</v>
+      </c>
+      <c r="E12" t="str">
+        <v>aperta</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0 / 10</v>
+      </c>
+      <c r="G12" t="str">
+        <v>30/10/2026</v>
+      </c>
+      <c r="H12" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026/OC/00329</v>
+      </c>
+      <c r="B13" t="str">
+        <v>0050</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>EL50811EMAN022K3GD32390</v>
+      </c>
+      <c r="E13" t="str">
+        <v>aperta</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0 / 8</v>
+      </c>
+      <c r="G13" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="H13" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026/OC/00329</v>
+      </c>
+      <c r="B14" t="str">
+        <v>0060</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>EL50811EMAN03K3GD32260</v>
+      </c>
+      <c r="E14" t="str">
+        <v>completata</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0 / 1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>11/09/2026</v>
+      </c>
+      <c r="H14" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J14"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:A2"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" customWidth="1"/>
-    <col min="9" max="9" width="49.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Ordine</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Pos</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Stato qui</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Ordinate qui</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Spedite qui</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Restano qui</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Residua in Alnus</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Ordinate in Alnus</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Cosa fare</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Fatto?</v>
+        <v>(vuoto)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026/OC/00011</v>
-      </c>
-      <c r="B2" t="str">
-        <v>0010</v>
-      </c>
-      <c r="C2" t="str">
-        <v>completata</v>
-      </c>
-      <c r="D2">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>ALNUS non sa di una spedizione gia’ fatta.</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026/OC/00107</v>
-      </c>
-      <c r="B3" t="str">
-        <v>0010</v>
-      </c>
-      <c r="C3" t="str">
-        <v>aperta</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>GESTIONALE: manca una spedizione da registrare.</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026/OC/00107</v>
-      </c>
-      <c r="B4" t="str">
-        <v>0020</v>
-      </c>
-      <c r="C4" t="str">
-        <v>completata</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>ALNUS non sa di una spedizione gia’ fatta.</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026/OC/00107</v>
-      </c>
-      <c r="B5" t="str">
-        <v>0040</v>
-      </c>
-      <c r="C5" t="str">
-        <v>aperta</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>GESTIONALE: manca una spedizione da registrare.</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>niente da segnalare</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1244,11 +1243,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" customWidth="1"/>
@@ -1346,124 +1345,66 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026/OC/00155</v>
+        <v>2026/OC/00357</v>
       </c>
       <c r="B4" t="str">
         <v>0010</v>
       </c>
       <c r="C4" t="str">
-        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
+        <v>Elcotec S.r.l.</v>
       </c>
       <c r="D4" t="str">
-        <v>SP-TFS01286800</v>
+        <v>EL50212MECB00000008220</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
         <v>aperta</v>
       </c>
       <c r="G4" t="str">
-        <v>12/06/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="H4">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="I4" t="str">
-        <v>0 / 10</v>
+        <v>0 / 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026/OC/00155</v>
+        <v>2026/OC/00326</v>
       </c>
       <c r="B5" t="str">
-        <v>0020</v>
+        <v>0030</v>
       </c>
       <c r="C5" t="str">
-        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
+        <v>Tema Sinergie S.p.a.</v>
       </c>
       <c r="D5" t="str">
-        <v>SP-TF1287894</v>
+        <v>TS-342010003</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F5" t="str">
         <v>aperta</v>
       </c>
       <c r="G5" t="str">
-        <v>12/06/2026</v>
+        <v>06/08/2026</v>
       </c>
       <c r="H5">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I5" t="str">
-        <v>0 / 10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026/OC/00357</v>
-      </c>
-      <c r="B6" t="str">
-        <v>0010</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Elcotec S.r.l.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>EL50212MECB00000008220</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="str">
-        <v>aperta</v>
-      </c>
-      <c r="G6" t="str">
-        <v>23/07/2026</v>
-      </c>
-      <c r="H6">
-        <v>36</v>
-      </c>
-      <c r="I6" t="str">
-        <v>0 / 1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026/OC/00326</v>
-      </c>
-      <c r="B7" t="str">
-        <v>0030</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Tema Sinergie S.p.a.</v>
-      </c>
-      <c r="D7" t="str">
-        <v>TS-342010003</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7" t="str">
-        <v>aperta</v>
-      </c>
-      <c r="G7" t="str">
-        <v>06/08/2026</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7" t="str">
         <v>0 / 15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:I5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/strumenti/anomalie-28ago.xlsx
+++ b/strumenti/anomalie-28ago.xlsx
@@ -11,7 +11,7 @@
     <sheet name="5 In ritardo" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'1 Stati'!A1:J14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'1 Stati'!A1:J16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'3 Senza codice'!A1:I5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'5 In ritardo'!A1:I5</definedName>
   </definedNames>
@@ -474,7 +474,7 @@
         <v>1 Stati</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="str">
         <v>I due sistemi non concordano su cosa sia finito. E’ il gruppo da sistemare per primo.</v>
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -859,28 +859,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026/OC/00209</v>
+        <v>2026/OC/00195</v>
       </c>
       <c r="B10" t="str">
         <v>0020</v>
       </c>
       <c r="C10" t="str">
-        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
+        <v>SENZANI BREVETTI S.p.a.</v>
       </c>
       <c r="D10" t="str">
-        <v>SP-GD2587807</v>
+        <v>SZ-A09103_BOX</v>
       </c>
       <c r="E10" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F10" t="str">
-        <v>0 / 5</v>
+        <v>0 / 1</v>
       </c>
       <c r="G10" t="str">
-        <v>28/08/2026</v>
+        <v>12/09/2026</v>
       </c>
       <c r="H10" t="str">
-        <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
+        <v>KIT A09103: in Alnus non resta nessuna delle sue righe</v>
       </c>
       <c r="I10" t="str">
         <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
@@ -891,28 +891,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026/OC/00216</v>
+        <v>2026/OC/00202</v>
       </c>
       <c r="B11" t="str">
-        <v>0010</v>
+        <v>0020</v>
       </c>
       <c r="C11" t="str">
-        <v>Elcotec S.r.l.</v>
+        <v>SENZANI BREVETTI S.p.a.</v>
       </c>
       <c r="D11" t="str">
-        <v>EL50811EMAN003K3GD40550</v>
+        <v>SZ-D34807_BOX</v>
       </c>
       <c r="E11" t="str">
-        <v>aperta</v>
+        <v>completata</v>
       </c>
       <c r="F11" t="str">
-        <v>0 / 30</v>
+        <v>0 / 1</v>
       </c>
       <c r="G11" t="str">
-        <v>30/10/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+        <v>KIT D34807: in Alnus non resta nessuna delle sue righe</v>
       </c>
       <c r="I11" t="str">
         <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
@@ -923,28 +923,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026/OC/00216</v>
+        <v>2026/OC/00209</v>
       </c>
       <c r="B12" t="str">
         <v>0020</v>
       </c>
       <c r="C12" t="str">
-        <v>Elcotec S.r.l.</v>
+        <v>Sacmi Packaging &amp; Chocolate S.p.a.</v>
       </c>
       <c r="D12" t="str">
-        <v>EL50811EMANCR3K3GD41410</v>
+        <v>SP-GD2587807</v>
       </c>
       <c r="E12" t="str">
         <v>aperta</v>
       </c>
       <c r="F12" t="str">
-        <v>0 / 10</v>
+        <v>0 / 5</v>
       </c>
       <c r="G12" t="str">
-        <v>30/10/2026</v>
+        <v>28/08/2026</v>
       </c>
       <c r="H12" t="str">
-        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+        <v>per Alnus FINITA (l’ordine c’e ancora, e’ sparita la riga)</v>
       </c>
       <c r="I12" t="str">
         <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
@@ -955,25 +955,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026/OC/00329</v>
+        <v>2026/OC/00216</v>
       </c>
       <c r="B13" t="str">
-        <v>0050</v>
+        <v>0010</v>
       </c>
       <c r="C13" t="str">
         <v>Elcotec S.r.l.</v>
       </c>
       <c r="D13" t="str">
-        <v>EL50811EMAN022K3GD32390</v>
+        <v>EL50811EMAN003K3GD40550</v>
       </c>
       <c r="E13" t="str">
         <v>aperta</v>
       </c>
       <c r="F13" t="str">
-        <v>0 / 8</v>
+        <v>0 / 30</v>
       </c>
       <c r="G13" t="str">
-        <v>02/09/2026</v>
+        <v>30/10/2026</v>
       </c>
       <c r="H13" t="str">
         <v>per Alnus FINITA (sparito tutto l’ordine)</v>
@@ -987,25 +987,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026/OC/00329</v>
+        <v>2026/OC/00216</v>
       </c>
       <c r="B14" t="str">
-        <v>0060</v>
+        <v>0020</v>
       </c>
       <c r="C14" t="str">
         <v>Elcotec S.r.l.</v>
       </c>
       <c r="D14" t="str">
-        <v>EL50811EMAN03K3GD32260</v>
+        <v>EL50811EMANCR3K3GD41410</v>
       </c>
       <c r="E14" t="str">
-        <v>completata</v>
+        <v>aperta</v>
       </c>
       <c r="F14" t="str">
-        <v>0 / 1</v>
+        <v>0 / 10</v>
       </c>
       <c r="G14" t="str">
-        <v>11/09/2026</v>
+        <v>30/10/2026</v>
       </c>
       <c r="H14" t="str">
         <v>per Alnus FINITA (sparito tutto l’ordine)</v>
@@ -1017,10 +1017,74 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026/OC/00329</v>
+      </c>
+      <c r="B15" t="str">
+        <v>0050</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>EL50811EMAN022K3GD32390</v>
+      </c>
+      <c r="E15" t="str">
+        <v>aperta</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0 / 8</v>
+      </c>
+      <c r="G15" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="H15" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026/OC/00329</v>
+      </c>
+      <c r="B16" t="str">
+        <v>0060</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Elcotec S.r.l.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>EL50811EMAN03K3GD32260</v>
+      </c>
+      <c r="E16" t="str">
+        <v>completata</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0 / 1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>11/09/2026</v>
+      </c>
+      <c r="H16" t="str">
+        <v>per Alnus FINITA (sparito tutto l’ordine)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Se e’ partita: registrare la spedizione QUI (lo stato va a spedita da solo). Se non e’ partita: riaprirla in ALNUS.</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J16"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
